--- a/registration_forms/050_fundraiser_check_in_form--registration_forms.xlsx
+++ b/registration_forms/050_fundraiser_check_in_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'attendee'}</t>
+          <t>attendee</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Attendee'}</t>
+          <t>Attendee</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'organizer'}</t>
+          <t>organizer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Organizer'}</t>
+          <t>Organizer</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'speaker'}</t>
+          <t>speaker</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Speaker'}</t>
+          <t>Speaker</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'fundraiser'}</t>
+          <t>fundraiser</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Fundraiser'}</t>
+          <t>Fundraiser</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'event'}</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Event'}</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'registration'}</t>
+          <t>registration</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Registration'}</t>
+          <t>Registration</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'fundraiser'}</t>
+          <t>fundraiser</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Fundraiser'}</t>
+          <t>Fundraiser</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'event'}</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Event'}</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'registration'}</t>
+          <t>registration</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Registration'}</t>
+          <t>Registration</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy2'}</t>
+          <t>chatjimmy2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'chatjimmy2'}</t>
+          <t>chatjimmy2</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy3'}</t>
+          <t>chatjimmy3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'chatjimmy3'}</t>
+          <t>chatjimmy3</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'050_fundraiser_check_in_form--registration_forms'}</t>
+          <t>050_fundraiser_check_in_form--registration_forms</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': '050_fundraiser_check_in_form--registration_forms'}</t>
+          <t>050 fundraiser check in form--registration forms</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'050_fundraiser_check_in_form--forms'}</t>
+          <t>050_fundraiser_check_in_form--forms</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': '050_fundraiser_check_in_form--forms'}</t>
+          <t>050 fundraiser check in form--forms</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'050_fundraiser_check_in_form--forms_2'}</t>
+          <t>050_fundraiser_check_in_form--forms_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': '050_fundraiser_check_in_form--forms_2'}</t>
+          <t>050 fundraiser check in form--forms 2</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'/path/to/output1'}</t>
+          <t>/path/to/output1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': '/path/to/output1'}</t>
+          <t>/path/to/output1</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'/path/to/output2'}</t>
+          <t>/path/to/output2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': '/path/to/output2'}</t>
+          <t>/path/to/output2</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'/path/to/output3'}</t>
+          <t>/path/to/output3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': '/path/to/output3'}</t>
+          <t>/path/to/output3</t>
         </is>
       </c>
     </row>
